--- a/output/北塩原村_打合せ論点_10項目.xlsx
+++ b/output/北塩原村_打合せ論点_10項目.xlsx
@@ -2713,7 +2713,7 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <t>家族の休息を実際に成り立たせるには、預かる先があることだけでは足りません。本人が家族以外の方から医療的ケアを受けることに…
-家族以外の担い手については、担える方の要件を踏まえて確保します。喀痰の吸引等は、医師及び看護職員のほか、登録を受けた研修…
+家族以外の担い手については、担える方の要件を踏まえて確保します。喀痰の吸引等は、医師及び看護職員のほか、介護の職員等が医…
 災害時の医療の継続については、電源の確保を具体の備えまで進めます。人工呼吸器及び吸引器について、内蔵の電池で動く時間、外…
 【注記】【村へ確認（Ｍ-120）】医療的ケアについて、①村内及び圏域に喀痰吸引等の研修を修了して認定を受けた方がいるか（人数、所…</t>
         </is>
@@ -2743,7 +2743,7 @@
       <c r="E7" s="9" t="inlineStr">
         <is>
           <t>⑥の指標「個別避難計画の策定件数」は、現状１件に対して令和11年度に10件を目標としています。計画を10件作るためには、…
-第一に、避難行動要支援者名簿の整備です。名簿に掲載される方の範囲と、名簿を平常時から避難支援等関係者に提供することへの同…
+第一に、避難行動要支援者名簿の整備です。名簿の作成は市町村の義務であり、個別避難計画の作成は努力義務です（第１章２）。義…
 訓練は、回数だけでは実効を測れません。毎年度の点検評価（第１章６）では、実施した回数に加えて、障がいのある方の参加者数、…
 【注記】【村へ確認（Ｍ-119）】①避難行動要支援者名簿の掲載者数、平常時からの提供に同意している方の人数、及び名簿を提供してい…</t>
         </is>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>就労の支援を進めるうえで、本村の事業主の構えを踏まえる必要があります。障害者雇用率による雇用の義務は、常時雇用する労働者…
+          <t>就労の支援を進めるうえで、本村の事業主の構えを踏まえる必要があります。障害者雇用率による雇用の義務がかかる事業主の範囲は…
 入口としては、就労選択支援を用います。就労選択支援は、令和９年４月から就労継続支援Ａ型等の新規の利用時に原則として利用す…
 【注記】【村へ確認（Ｍ-121）】①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）、②村役場…</t>
         </is>

--- a/output/北塩原村_打合せ論点_10項目.xlsx
+++ b/output/北塩原村_打合せ論点_10項目.xlsx
@@ -2973,7 +2973,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>令和８年10月13日の打合せ論点⑩に関わるものです。本村には就労移行支援の事業所がなく、一般就労の支援はハローワーク等との連携により進める整理としています。進め方は、村内の事業主の構えによって変わります。次をご確認ください。①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）。②村役場（村長部局及び教育委員会）の障がいのある方の雇用の状況。③農業・観光業の現場で障がいのある方が就労した例があるか（農福連携の取組みを含む）。④ハローワーク（会津若松公共職業安定所）、福島県障害者職業センター、障害者就業・生活支援センターへつないだ件数（令和６年度・令和７年度）。①が「ない」である場合は、雇用率を軸にした施策ではなく、義務のかからない規模の事業主への働きかけと農福連携に重点を置く形で計画に書きます。</t>
+          <t>令和８年10月13日の打合せ論点⑩に関わるものです。本村には就労移行支援の事業所がなく、一般就労の支援はハローワーク等との連携により進める整理としています。進め方は、村内の事業主の構えによって変わります。次をご確認ください。①村内に障害者雇用率による雇用の義務がかかる規模の事業主があるか（ある場合はその数）。②村役場（村長部局及び教育委員会）及び村の関係団体（社会福祉協議会等）の障がいのある方の雇用の状況（第4次北塩原村障がい者計画の②公共団体への雇用促進は「村及び村関係団体等における事務や作業など」を対象としています）。③農業・観光業の現場で障がいのある方が就労した例があるか（農福連携の取組みを含む）。④ハローワーク（会津若松公共職業安定所）、福島県障害者職業センター、障害者就業・生活支援センターへつないだ件数（令和６年度・令和７年度）。①が「ない」である場合は、雇用率を軸にした施策ではなく、義務のかからない規模の事業主への働きかけと農福連携に重点を置く形で計画に書きます。</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
